--- a/готовое_решение/тест/04_подтвержденный_прогресс/вход.xlsx
+++ b/готовое_решение/тест/04_подтвержденный_прогресс/вход.xlsx
@@ -172,6 +172,11 @@
           <t>Конкурсы</t>
         </is>
       </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Статус без выбора</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
